--- a/Seminarios/TablaComparativaRadar.xlsx
+++ b/Seminarios/TablaComparativaRadar.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utrujillo/Documents/Develops/Python/Python3/Vision/analyze_posture_estimation/Seminarios/SeminarioIV/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utrujillo/Documents/Develops/Python/Python3/Vision/analyze_posture_estimation/Seminarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216F0B4C-C5A8-F248-8A6A-FABD9DAC1461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A28798-443A-494A-8585-B1C203B1956B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="740" windowWidth="25780" windowHeight="16760" activeTab="1" xr2:uid="{0E2D49C4-014D-F645-895F-A57D6B41FEED}"/>
+    <workbookView xWindow="40640" yWindow="700" windowWidth="25780" windowHeight="16760" activeTab="1" xr2:uid="{0E2D49C4-014D-F645-895F-A57D6B41FEED}"/>
   </bookViews>
   <sheets>
     <sheet name="SIV" sheetId="1" r:id="rId1"/>
@@ -1034,6 +1034,18 @@
       <c r="B2">
         <v>0.1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1042,6 +1054,18 @@
       <c r="B3">
         <v>0.5</v>
       </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1050,6 +1074,18 @@
       <c r="B4">
         <v>0.9</v>
       </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1058,6 +1094,18 @@
       <c r="B5">
         <v>0.1</v>
       </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1066,6 +1114,18 @@
       <c r="B6">
         <v>0.5</v>
       </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1074,6 +1134,18 @@
       <c r="B7">
         <v>0.9</v>
       </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1082,6 +1154,18 @@
       <c r="B8">
         <v>0.1</v>
       </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1090,6 +1174,18 @@
       <c r="B9">
         <v>0.5</v>
       </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1098,6 +1194,18 @@
       <c r="B10">
         <v>0.9</v>
       </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1106,6 +1214,18 @@
       <c r="B11">
         <v>0.1</v>
       </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -1114,6 +1234,18 @@
       <c r="B12">
         <v>0.5</v>
       </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1122,6 +1254,18 @@
       <c r="B13">
         <v>0.9</v>
       </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -1130,6 +1274,18 @@
       <c r="B14">
         <v>0.1</v>
       </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1138,6 +1294,18 @@
       <c r="B15">
         <v>0.5</v>
       </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1146,140 +1314,332 @@
       <c r="B16">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>9</v>
       </c>
       <c r="B18">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>10</v>
       </c>
       <c r="B21">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>10</v>
       </c>
       <c r="B22">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>11</v>
       </c>
       <c r="B23">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>11</v>
       </c>
       <c r="B24">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>11</v>
       </c>
       <c r="B25">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>13</v>
       </c>
       <c r="B29">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>13</v>
       </c>
       <c r="B30">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>13</v>
       </c>
       <c r="B31">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>14</v>
       </c>
       <c r="B32">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>14</v>
       </c>
       <c r="B33">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>14</v>
       </c>
       <c r="B34">
         <v>0.9</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
